--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703160</v>
+        <v>113703163</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>57490</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>103056</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750835</v>
+        <v>750819</v>
       </c>
       <c r="R3" t="n">
-        <v>7189239</v>
+        <v>7189208</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703164</v>
+        <v>113703166</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750751</v>
+        <v>750734</v>
       </c>
       <c r="R4" t="n">
-        <v>7189131</v>
+        <v>7189207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703163</v>
+        <v>113703167</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,43 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103056</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750819</v>
+        <v>750777</v>
       </c>
       <c r="R5" t="n">
-        <v>7189208</v>
+        <v>7189269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703167</v>
+        <v>113703160</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750777</v>
+        <v>750835</v>
       </c>
       <c r="R6" t="n">
-        <v>7189269</v>
+        <v>7189239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703166</v>
+        <v>113703164</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750734</v>
+        <v>750751</v>
       </c>
       <c r="R7" t="n">
-        <v>7189207</v>
+        <v>7189131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703163</v>
+        <v>113703160</v>
       </c>
       <c r="B3" t="n">
-        <v>57490</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,43 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103056</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750819</v>
+        <v>750835</v>
       </c>
       <c r="R3" t="n">
-        <v>7189208</v>
+        <v>7189239</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703166</v>
+        <v>113703164</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -938,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750734</v>
+        <v>750751</v>
       </c>
       <c r="R4" t="n">
-        <v>7189207</v>
+        <v>7189131</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703167</v>
+        <v>113703163</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>57490</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,34 +1012,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103056</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750777</v>
+        <v>750819</v>
       </c>
       <c r="R5" t="n">
-        <v>7189269</v>
+        <v>7189208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703160</v>
+        <v>113703167</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750835</v>
+        <v>750777</v>
       </c>
       <c r="R6" t="n">
-        <v>7189239</v>
+        <v>7189269</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703164</v>
+        <v>113703166</v>
       </c>
       <c r="B7" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750751</v>
+        <v>750734</v>
       </c>
       <c r="R7" t="n">
-        <v>7189131</v>
+        <v>7189207</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113703165</v>
+        <v>113703167</v>
       </c>
       <c r="B2" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750764</v>
+        <v>750777</v>
       </c>
       <c r="R2" t="n">
-        <v>7189132</v>
+        <v>7189269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703160</v>
+        <v>113703165</v>
       </c>
       <c r="B3" t="n">
         <v>81944</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750835</v>
+        <v>750764</v>
       </c>
       <c r="R3" t="n">
-        <v>7189239</v>
+        <v>7189132</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703164</v>
+        <v>113703163</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,34 +905,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>103056</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750751</v>
+        <v>750819</v>
       </c>
       <c r="R4" t="n">
-        <v>7189131</v>
+        <v>7189208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703163</v>
+        <v>113703164</v>
       </c>
       <c r="B5" t="n">
-        <v>57490</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,43 +1021,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103056</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750819</v>
+        <v>750751</v>
       </c>
       <c r="R5" t="n">
-        <v>7189208</v>
+        <v>7189131</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703167</v>
+        <v>113703160</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750777</v>
+        <v>750835</v>
       </c>
       <c r="R6" t="n">
-        <v>7189269</v>
+        <v>7189239</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113703167</v>
+        <v>113703163</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>57490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,43 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103056</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750777</v>
+        <v>750819</v>
       </c>
       <c r="R2" t="n">
-        <v>7189269</v>
+        <v>7189208</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703165</v>
+        <v>113703166</v>
       </c>
       <c r="B3" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750764</v>
+        <v>750734</v>
       </c>
       <c r="R3" t="n">
-        <v>7189132</v>
+        <v>7189207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703163</v>
+        <v>113703160</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,43 +914,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103056</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750819</v>
+        <v>750835</v>
       </c>
       <c r="R4" t="n">
-        <v>7189208</v>
+        <v>7189239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703164</v>
+        <v>113703167</v>
       </c>
       <c r="B5" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750751</v>
+        <v>750777</v>
       </c>
       <c r="R5" t="n">
-        <v>7189131</v>
+        <v>7189269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703160</v>
+        <v>113703164</v>
       </c>
       <c r="B6" t="n">
         <v>81944</v>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750835</v>
+        <v>750751</v>
       </c>
       <c r="R6" t="n">
-        <v>7189239</v>
+        <v>7189131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703166</v>
+        <v>113703165</v>
       </c>
       <c r="B7" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750734</v>
+        <v>750764</v>
       </c>
       <c r="R7" t="n">
-        <v>7189207</v>
+        <v>7189132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113703163</v>
+        <v>113703160</v>
       </c>
       <c r="B2" t="n">
-        <v>57490</v>
+        <v>81944</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,43 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103056</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750819</v>
+        <v>750835</v>
       </c>
       <c r="R2" t="n">
-        <v>7189208</v>
+        <v>7189239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -791,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703166</v>
+        <v>113703167</v>
       </c>
       <c r="B3" t="n">
         <v>78201</v>
@@ -831,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750734</v>
+        <v>750777</v>
       </c>
       <c r="R3" t="n">
-        <v>7189207</v>
+        <v>7189269</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -898,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703160</v>
+        <v>113703163</v>
       </c>
       <c r="B4" t="n">
-        <v>81944</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,34 +905,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>103056</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750835</v>
+        <v>750819</v>
       </c>
       <c r="R4" t="n">
-        <v>7189239</v>
+        <v>7189208</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703167</v>
+        <v>113703165</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750777</v>
+        <v>750764</v>
       </c>
       <c r="R5" t="n">
-        <v>7189269</v>
+        <v>7189132</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703164</v>
+        <v>113703166</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750751</v>
+        <v>750734</v>
       </c>
       <c r="R6" t="n">
-        <v>7189131</v>
+        <v>7189207</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703165</v>
+        <v>113703164</v>
       </c>
       <c r="B7" t="n">
         <v>81944</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750764</v>
+        <v>750751</v>
       </c>
       <c r="R7" t="n">
-        <v>7189132</v>
+        <v>7189131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -1005,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703165</v>
+        <v>113703166</v>
       </c>
       <c r="B5" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,21 +1021,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750764</v>
+        <v>750734</v>
       </c>
       <c r="R5" t="n">
-        <v>7189132</v>
+        <v>7189207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703166</v>
+        <v>113703165</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,21 +1128,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750734</v>
+        <v>750764</v>
       </c>
       <c r="R6" t="n">
-        <v>7189207</v>
+        <v>7189132</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113703160</v>
+        <v>113703166</v>
       </c>
       <c r="B2" t="n">
-        <v>81944</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750835</v>
+        <v>750734</v>
       </c>
       <c r="R2" t="n">
-        <v>7189239</v>
+        <v>7189207</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703167</v>
+        <v>113703164</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>81944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750777</v>
+        <v>750751</v>
       </c>
       <c r="R3" t="n">
-        <v>7189269</v>
+        <v>7189131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113703163</v>
+        <v>113703160</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>81944</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,43 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103056</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750819</v>
+        <v>750835</v>
       </c>
       <c r="R4" t="n">
-        <v>7189208</v>
+        <v>7189239</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703166</v>
+        <v>113703167</v>
       </c>
       <c r="B5" t="n">
         <v>78201</v>
@@ -1045,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750734</v>
+        <v>750777</v>
       </c>
       <c r="R5" t="n">
-        <v>7189207</v>
+        <v>7189269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703165</v>
+        <v>113703163</v>
       </c>
       <c r="B6" t="n">
-        <v>81944</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1128,34 +1119,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>103056</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bjurbäcken, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750764</v>
+        <v>750819</v>
       </c>
       <c r="R6" t="n">
-        <v>7189132</v>
+        <v>7189208</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113703164</v>
+        <v>113703165</v>
       </c>
       <c r="B7" t="n">
         <v>81944</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750751</v>
+        <v>750764</v>
       </c>
       <c r="R7" t="n">
-        <v>7189131</v>
+        <v>7189132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113703166</v>
+        <v>113703160</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750734</v>
+        <v>750834</v>
       </c>
       <c r="R2" t="n">
-        <v>7189206</v>
+        <v>7189239</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113703160</v>
+        <v>113703164</v>
       </c>
       <c r="B3" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750834</v>
+        <v>750751</v>
       </c>
       <c r="R3" t="n">
-        <v>7189239</v>
+        <v>7189131</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,12 +882,7 @@
         <v>113703165</v>
       </c>
       <c r="B4" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113703167</v>
+        <v>113703166</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750777</v>
+        <v>750734</v>
       </c>
       <c r="R5" t="n">
-        <v>7189269</v>
+        <v>7189206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,37 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113703164</v>
+        <v>113703167</v>
       </c>
       <c r="B6" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750751</v>
+        <v>750777</v>
       </c>
       <c r="R6" t="n">
-        <v>7189131</v>
+        <v>7189269</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,16 +1188,11 @@
         <v>113703163</v>
       </c>
       <c r="B7" t="n">
-        <v>57952</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">

--- a/artfynd/A 44152-2023 artfynd.xlsx
+++ b/artfynd/A 44152-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703160</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703164</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703165</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703166</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703167</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,8 +1323,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113703163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>